--- a/artfynd/Kilkojan artfynd.xlsx
+++ b/artfynd/Kilkojan artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110815719</v>
+        <v>16895610</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,42 +1024,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 450 m SO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465538</v>
+        <v>465354</v>
       </c>
       <c r="R5" t="n">
-        <v>6923829</v>
+        <v>6923881</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,37 +1095,39 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre lavtallskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>1 substratenheter # gammal tallump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16895610</v>
+        <v>16895612</v>
       </c>
       <c r="B6" t="n">
         <v>78993</v>
@@ -1161,14 +1158,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 450 m SO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 500 m SO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465354</v>
+        <v>465453</v>
       </c>
       <c r="R6" t="n">
-        <v>6923881</v>
+        <v>6923936</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,7 +1219,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallump</t>
+          <t>1 substratenheter # grov, fallen tallhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1244,45 +1241,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16895612</v>
+        <v>16895613</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>92509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 500 m SO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 450 m Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465453</v>
+        <v>465566</v>
       </c>
       <c r="R7" t="n">
-        <v>6923936</v>
+        <v>6924248</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1325,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>äldre lavtallskog</t>
+          <t>bäckklyfta med gammal barrblandskog</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1336,7 +1333,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov, fallen tallhögstubbe</t>
+          <t>1 substratenheter # mkt gammal sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1358,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16895613</v>
+        <v>16895611</v>
       </c>
       <c r="B8" t="n">
-        <v>92509</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 450 m Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 450 m SO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465566</v>
+        <v>465365</v>
       </c>
       <c r="R8" t="n">
-        <v>6924248</v>
+        <v>6923871</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1439,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>bäckklyfta med gammal barrblandskog</t>
+          <t>äldre lavtallskog</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1450,7 +1447,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # mkt gammal sälg</t>
+          <t>1 substratenheter # gammal tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1472,48 +1469,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16895611</v>
+        <v>110815719</v>
       </c>
       <c r="B9" t="n">
-        <v>92083</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 450 m SO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465365</v>
+        <v>465538</v>
       </c>
       <c r="R9" t="n">
-        <v>6923871</v>
+        <v>6923829</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,12 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,35 +1556,33 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre lavtallskog</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3068,7 +3068,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16895636</v>
+        <v>16895632</v>
       </c>
       <c r="B23" t="n">
         <v>78993</v>
@@ -3099,14 +3099,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 600 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 500 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465429</v>
+        <v>465239</v>
       </c>
       <c r="R23" t="n">
-        <v>6924707</v>
+        <v>6924737</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3152,15 +3152,15 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>blockig, ljus nordvänd tallnaturskog</t>
+          <t>tallnaturskog i västvänd moränbacke</t>
         </is>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>2 substratenheter # grov gammal fallen torrak</t>
+          <t>1 substratenheter # grov gammal fälld torrak</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16895630</v>
+        <v>16895633</v>
       </c>
       <c r="B24" t="n">
-        <v>79406</v>
+        <v>78993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,34 +3193,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 500 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 550 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465192</v>
+        <v>465331</v>
       </c>
       <c r="R24" t="n">
-        <v>6924731</v>
+        <v>6924738</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>gles och senvuxen fuktskog</t>
+          <t>blockig, ljus nordvänd tallnaturskog</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>3 substratenheter # klen gammal gran</t>
+          <t>3 substratenheter # gammal fallen topp av torrak och lutande sådana</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16895601</v>
+        <v>16895636</v>
       </c>
       <c r="B25" t="n">
-        <v>81312</v>
+        <v>78993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,34 +3307,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 400 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 600 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465419</v>
+        <v>465429</v>
       </c>
       <c r="R25" t="n">
-        <v>6924534</v>
+        <v>6924707</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3380,15 +3380,15 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>olikåldrig lingontallskog</t>
+          <t>blockig, ljus nordvänd tallnaturskog</t>
         </is>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammalgrov och hög tallhögstubbe</t>
+          <t>2 substratenheter # grov gammal fallen torrak</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3410,45 +3410,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16895589</v>
+        <v>16895630</v>
       </c>
       <c r="B26" t="n">
-        <v>92083</v>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 150 m N om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 500 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465119</v>
+        <v>465192</v>
       </c>
       <c r="R26" t="n">
-        <v>6924400</v>
+        <v>6924731</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,15 +3494,15 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>äldre blåbärstallskog</t>
+          <t>gles och senvuxen fuktskog</t>
         </is>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga</t>
+          <t>3 substratenheter # klen gammal gran</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3524,45 +3524,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16895596</v>
+        <v>16895601</v>
       </c>
       <c r="B27" t="n">
-        <v>92083</v>
+        <v>81312</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 450 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 400 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465329</v>
+        <v>465419</v>
       </c>
       <c r="R27" t="n">
-        <v>6924602</v>
+        <v>6924534</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>olikåldrig blåbärstallskog</t>
+          <t>olikåldrig lingontallskog</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal rödmurken tallåga</t>
+          <t>1 substratenheter # gammalgrov och hög tallhögstubbe</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16895598</v>
+        <v>16895589</v>
       </c>
       <c r="B28" t="n">
         <v>92083</v>
@@ -3669,14 +3669,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 460 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 150 m N om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465367</v>
+        <v>465119</v>
       </c>
       <c r="R28" t="n">
-        <v>6924601</v>
+        <v>6924400</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>olikåldrig blåbärstallskog</t>
+          <t>äldre blåbärstallskog</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal rödmurken tallåga</t>
+          <t>1 substratenheter # grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16895603</v>
+        <v>16895596</v>
       </c>
       <c r="B29" t="n">
         <v>92083</v>
@@ -3783,14 +3783,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 250 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 450 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465229</v>
+        <v>465329</v>
       </c>
       <c r="R29" t="n">
-        <v>6924419</v>
+        <v>6924602</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal tallåga</t>
+          <t>1 substratenheter # gammal rödmurken tallåga</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3866,45 +3866,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16895594</v>
+        <v>16895598</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>92083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 420 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 460 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465273</v>
+        <v>465367</v>
       </c>
       <c r="R30" t="n">
-        <v>6924603</v>
+        <v>6924601</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>1 substratenheter # på grov gammal tallhögstubbe</t>
+          <t>1 substratenheter # gammal rödmurken tallåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3980,45 +3980,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16895597</v>
+        <v>16895603</v>
       </c>
       <c r="B31" t="n">
-        <v>78730</v>
+        <v>92083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 450 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 250 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465345</v>
+        <v>465229</v>
       </c>
       <c r="R31" t="n">
-        <v>6924598</v>
+        <v>6924419</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>olikåldrig lingontallskog</t>
+          <t>olikåldrig blåbärstallskog</t>
         </is>
       </c>
       <c r="AN31" t="n">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallhögstubbe</t>
+          <t>1 substratenheter # grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16895592</v>
+        <v>16895634</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>91962</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4105,34 +4105,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 300 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 550 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465219</v>
+        <v>465331</v>
       </c>
       <c r="R32" t="n">
-        <v>6924545</v>
+        <v>6924738</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>olikåldrig blåbärstallskog</t>
+          <t>blockig, ljus nordvänd tallnaturskog</t>
         </is>
       </c>
       <c r="AN32" t="n">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>1 substratenheter # kol på gammal tallhögstubbe</t>
+          <t>1 substratenheter # gammal fallen topp av torrak</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16895608</v>
+        <v>16895635</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>91831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4219,34 +4219,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 500 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 600 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465435</v>
+        <v>465382</v>
       </c>
       <c r="R33" t="n">
-        <v>6924435</v>
+        <v>6924757</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>olikåldrig stavgtallskog</t>
+          <t>blockig, ljus nordvänd tallnaturskog</t>
         </is>
       </c>
       <c r="AN33" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>1 substratenheter # mkt grov torraka med spår av 4 bränder</t>
+          <t>1 substratenheter # klen, hård tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16895600</v>
+        <v>16895594</v>
       </c>
       <c r="B34" t="n">
-        <v>78334</v>
+        <v>78730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4333,34 +4333,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 400 m NO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 420 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465419</v>
+        <v>465273</v>
       </c>
       <c r="R34" t="n">
-        <v>6924534</v>
+        <v>6924603</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>olikåldrig lingontallskog</t>
+          <t>olikåldrig blåbärstallskog</t>
         </is>
       </c>
       <c r="AN34" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammalgrov och hög tallhögstubbe</t>
+          <t>1 substratenheter # på grov gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4436,10 +4436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16895856</v>
+        <v>16895597</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>78730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4447,34 +4447,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 250 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 450 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465155</v>
+        <v>465345</v>
       </c>
       <c r="R35" t="n">
-        <v>6924463</v>
+        <v>6924598</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>olikåldrig blåbärstallskog</t>
+          <t>olikåldrig lingontallskog</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>1 substratenheter # kol på grov gammal tallhögstubbe</t>
+          <t>1 substratenheter # gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16895632</v>
+        <v>16895592</v>
       </c>
       <c r="B36" t="n">
-        <v>78993</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,34 +4561,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 500 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 300 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465239</v>
+        <v>465219</v>
       </c>
       <c r="R36" t="n">
-        <v>6924737</v>
+        <v>6924545</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>tallnaturskog i västvänd moränbacke</t>
+          <t>olikåldrig blåbärstallskog</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal fälld torrak</t>
+          <t>1 substratenheter # kol på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>16895633</v>
+        <v>16895608</v>
       </c>
       <c r="B37" t="n">
-        <v>78993</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4675,34 +4675,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 550 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 500 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465331</v>
+        <v>465435</v>
       </c>
       <c r="R37" t="n">
-        <v>6924738</v>
+        <v>6924435</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,15 +4748,15 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>blockig, ljus nordvänd tallnaturskog</t>
+          <t>olikåldrig stavgtallskog</t>
         </is>
       </c>
       <c r="AN37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>3 substratenheter # gammal fallen topp av torrak och lutande sådana</t>
+          <t>1 substratenheter # mkt grov torraka med spår av 4 bränder</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16895634</v>
+        <v>16895600</v>
       </c>
       <c r="B38" t="n">
-        <v>91962</v>
+        <v>78334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,34 +4789,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 550 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 400 m NO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465331</v>
+        <v>465419</v>
       </c>
       <c r="R38" t="n">
-        <v>6924738</v>
+        <v>6924534</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>blockig, ljus nordvänd tallnaturskog</t>
+          <t>olikåldrig lingontallskog</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal fallen topp av torrak</t>
+          <t>1 substratenheter # gammalgrov och hög tallhögstubbe</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16895635</v>
+        <v>16895856</v>
       </c>
       <c r="B39" t="n">
-        <v>91831</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4903,34 +4903,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 600 m NNO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 250 m NNO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465382</v>
+        <v>465155</v>
       </c>
       <c r="R39" t="n">
-        <v>6924757</v>
+        <v>6924463</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4957,12 +4957,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>blockig, ljus nordvänd tallnaturskog</t>
+          <t>olikåldrig blåbärstallskog</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>1 substratenheter # klen, hård tallåga</t>
+          <t>1 substratenheter # kol på grov gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16895621</v>
+        <v>110815726</v>
       </c>
       <c r="B40" t="n">
-        <v>92509</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5017,37 +5017,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 1000 m OSO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466012</v>
+        <v>465846</v>
       </c>
       <c r="R40" t="n">
-        <v>6923808</v>
+        <v>6923698</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,77 +5088,75 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>gammal, fuktig blandskog</t>
-        </is>
-      </c>
-      <c r="AN40" t="n">
-        <v>1</v>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16895623</v>
+        <v>16895619</v>
       </c>
       <c r="B41" t="n">
-        <v>92509</v>
+        <v>97358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 900 m SO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 900 m Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465836</v>
+        <v>465973</v>
       </c>
       <c r="R41" t="n">
-        <v>6923792</v>
+        <v>6924237</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5204,15 +5202,15 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>barnaturskog i nordbrant</t>
         </is>
       </c>
       <c r="AN41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>2 substratenheter # gamla grova tallågor</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5234,10 +5232,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110815722</v>
+        <v>16895620</v>
       </c>
       <c r="B42" t="n">
-        <v>80433</v>
+        <v>78993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,37 +5243,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 1000 m OSO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465804</v>
+        <v>466014</v>
       </c>
       <c r="R42" t="n">
-        <v>6923820</v>
+        <v>6923914</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5299,12 +5297,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5316,40 +5314,42 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>äldre stavatallskog</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>2</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>2 substratenheter # gamla tallågor</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110815724</v>
+        <v>16895624</v>
       </c>
       <c r="B43" t="n">
-        <v>80433</v>
+        <v>78993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,37 +5357,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 700 m Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465822</v>
+        <v>465777</v>
       </c>
       <c r="R43" t="n">
-        <v>6923823</v>
+        <v>6924244</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,40 +5428,42 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>äldre stavatallskog på nordvänd hällmark</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>1 substratenheter # fallen jättetorraka</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110815726</v>
+        <v>16895621</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>92509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5469,37 +5471,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 1000 m OSO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465846</v>
+        <v>466012</v>
       </c>
       <c r="R44" t="n">
-        <v>6923698</v>
+        <v>6923808</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5523,12 +5525,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5540,78 +5542,80 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>gammal, fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>1</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>1 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110815723</v>
+        <v>16895623</v>
       </c>
       <c r="B45" t="n">
-        <v>80432</v>
+        <v>92509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 900 m SO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465805</v>
+        <v>465836</v>
       </c>
       <c r="R45" t="n">
-        <v>6923821</v>
+        <v>6923792</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5635,12 +5639,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5652,40 +5656,42 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>1 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110815725</v>
+        <v>16895622</v>
       </c>
       <c r="B46" t="n">
-        <v>80432</v>
+        <v>79406</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,37 +5699,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 900 m OSO om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465822</v>
+        <v>465909</v>
       </c>
       <c r="R46" t="n">
-        <v>6923823</v>
+        <v>6923916</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5747,12 +5753,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,40 +5770,42 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>gammal, gles och fuktig blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>1 substratenheter # äldre björk</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16895619</v>
+        <v>16895617</v>
       </c>
       <c r="B47" t="n">
-        <v>97358</v>
+        <v>81312</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5805,34 +5813,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 900 m Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 1,1 km Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465973</v>
+        <v>466129</v>
       </c>
       <c r="R47" t="n">
-        <v>6924237</v>
+        <v>6924085</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5878,15 +5886,15 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>barnaturskog i nordbrant</t>
+          <t>tallnaturskog i nordbrant</t>
         </is>
       </c>
       <c r="AN47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>2 substratenheter # gamla grova tallågor</t>
+          <t>5 substratenheter # vitrötad kärnved på grova gamla torrakor och tallhögstubbar</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5908,45 +5916,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16895620</v>
+        <v>16895616</v>
       </c>
       <c r="B48" t="n">
-        <v>78993</v>
+        <v>92083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 1000 m OSO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 1,0 km Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466014</v>
+        <v>466072</v>
       </c>
       <c r="R48" t="n">
-        <v>6923914</v>
+        <v>6924213</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5992,15 +6000,15 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>äldre stavatallskog</t>
+          <t>tallnaturskog i nordsluttande hällmark</t>
         </is>
       </c>
       <c r="AN48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>2 substratenheter # gamla tallågor</t>
+          <t>1 substratenheter # klen gammal, marknära tallåga</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6022,45 +6030,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>16895624</v>
+        <v>16895618</v>
       </c>
       <c r="B49" t="n">
-        <v>78993</v>
+        <v>92083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 700 m Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, 900 m Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465777</v>
+        <v>465973</v>
       </c>
       <c r="R49" t="n">
-        <v>6924244</v>
+        <v>6924237</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6106,15 +6114,15 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>äldre stavatallskog på nordvänd hällmark</t>
+          <t>barnaturskog i nordbrant</t>
         </is>
       </c>
       <c r="AN49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>1 substratenheter # fallen jättetorraka</t>
+          <t>2 substratenheter # gamla grova tallågor</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6136,48 +6144,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>16895614</v>
+        <v>110815722</v>
       </c>
       <c r="B50" t="n">
-        <v>92509</v>
+        <v>80433</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 1,1 km Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466212</v>
+        <v>465804</v>
       </c>
       <c r="R50" t="n">
-        <v>6924253</v>
+        <v>6923820</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6201,12 +6209,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,42 +6226,40 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>äldre, lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN50" t="n">
-        <v>1</v>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>1 substratenheter # drygt 100-årig, avblåst sälg</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>16895622</v>
+        <v>110815724</v>
       </c>
       <c r="B51" t="n">
-        <v>79406</v>
+        <v>80433</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6261,37 +6267,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 900 m OSO om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465909</v>
+        <v>465822</v>
       </c>
       <c r="R51" t="n">
-        <v>6923916</v>
+        <v>6923823</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6315,12 +6321,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6332,42 +6338,40 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>gammal, gles och fuktig blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AN51" t="n">
-        <v>1</v>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre björk</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16895617</v>
+        <v>110815721</v>
       </c>
       <c r="B52" t="n">
-        <v>81312</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6375,37 +6379,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 1,1 km Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466129</v>
+        <v>465775</v>
       </c>
       <c r="R52" t="n">
-        <v>6924085</v>
+        <v>6923897</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6429,12 +6433,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6446,80 +6450,78 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>tallnaturskog i nordbrant</t>
-        </is>
-      </c>
-      <c r="AN52" t="n">
-        <v>5</v>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>5 substratenheter # vitrötad kärnved på grova gamla torrakor och tallhögstubbar</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16895616</v>
+        <v>110815723</v>
       </c>
       <c r="B53" t="n">
-        <v>92083</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 1,0 km Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466072</v>
+        <v>465805</v>
       </c>
       <c r="R53" t="n">
-        <v>6924213</v>
+        <v>6923821</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6543,12 +6545,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6560,80 +6562,78 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>tallnaturskog i nordsluttande hällmark</t>
-        </is>
-      </c>
-      <c r="AN53" t="n">
-        <v>1</v>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>1 substratenheter # klen gammal, marknära tallåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16895618</v>
+        <v>110815725</v>
       </c>
       <c r="B54" t="n">
-        <v>92083</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 900 m Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465973</v>
+        <v>465822</v>
       </c>
       <c r="R54" t="n">
-        <v>6924237</v>
+        <v>6923823</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,42 +6674,40 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>barnaturskog i nordbrant</t>
-        </is>
-      </c>
-      <c r="AN54" t="n">
-        <v>2</v>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>2 substratenheter # gamla grova tallågor</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16895615</v>
+        <v>110815720</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79917</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6717,37 +6715,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tvärhoberget, 1,1 km Ö om Kilkojan, Jmt</t>
+          <t>Tvärhoberget, Röjan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466216</v>
+        <v>465742</v>
       </c>
       <c r="R55" t="n">
-        <v>6924253</v>
+        <v>6923945</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6771,12 +6769,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6788,80 +6786,78 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>äldre, lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN55" t="n">
-        <v>1</v>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>1 substratenheter # kol på lutande tallhögstubbe</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>110815721</v>
+        <v>16895614</v>
       </c>
       <c r="B56" t="n">
-        <v>80432</v>
+        <v>92509</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 1,1 km Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465775</v>
+        <v>466212</v>
       </c>
       <c r="R56" t="n">
-        <v>6923897</v>
+        <v>6924253</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6885,12 +6881,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6902,40 +6898,42 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>äldre, lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN56" t="n">
+        <v>1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>1 substratenheter # drygt 100-årig, avblåst sälg</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>110815720</v>
+        <v>16895615</v>
       </c>
       <c r="B57" t="n">
-        <v>79917</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6943,37 +6941,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tvärhoberget, Röjan, Jmt</t>
+          <t>Tvärhoberget, 1,1 km Ö om Kilkojan, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465742</v>
+        <v>466216</v>
       </c>
       <c r="R57" t="n">
-        <v>6923945</v>
+        <v>6924253</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6997,12 +6995,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2014-05-15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7014,33 +7012,35 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>äldre, lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN57" t="n">
+        <v>1</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>1 substratenheter # kol på lutande tallhögstubbe</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
